--- a/Team-Data/2007-08/11-5-2007-08.xlsx
+++ b/Team-Data/2007-08/11-5-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -745,7 +812,7 @@
         <v>17</v>
       </c>
       <c r="AF2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
         <v>16</v>
@@ -784,7 +851,7 @@
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -924,7 +991,7 @@
         <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF3" t="n">
         <v>1</v>
@@ -960,7 +1027,7 @@
         <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>25</v>
@@ -969,7 +1036,7 @@
         <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>16</v>
@@ -978,10 +1045,10 @@
         <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>15</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1173,7 @@
         <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF4" t="n">
         <v>1</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1309,7 +1376,7 @@
         <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM5" t="n">
         <v>8</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>17</v>
@@ -1485,13 +1552,13 @@
         <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
         <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="n">
         <v>19</v>
@@ -1512,7 +1579,7 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1533,7 +1600,7 @@
         <v>16</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -1571,130 +1638,130 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="J7" t="n">
-        <v>73.8</v>
+        <v>72.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.505</v>
+        <v>0.518</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.378</v>
+        <v>0.357</v>
       </c>
       <c r="O7" t="n">
-        <v>22.5</v>
+        <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>25.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.882</v>
+        <v>0.851</v>
       </c>
       <c r="R7" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="S7" t="n">
-        <v>30.3</v>
+        <v>28.7</v>
       </c>
       <c r="T7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="U7" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="V7" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="W7" t="n">
         <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
         <v>7</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM7" t="n">
         <v>16</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR7" t="n">
         <v>29</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AT7" t="n">
         <v>28</v>
@@ -1703,25 +1770,25 @@
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>26</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -1831,22 +1898,22 @@
         <v>6.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>7</v>
       </c>
       <c r="AI8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ8" t="n">
         <v>8</v>
@@ -1870,7 +1937,7 @@
         <v>6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>10</v>
@@ -1888,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2052,13 +2119,13 @@
         <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
         <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT9" t="n">
         <v>19</v>
@@ -2073,10 +2140,10 @@
         <v>6</v>
       </c>
       <c r="AX9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-16.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2252,7 +2319,7 @@
         <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -2299,160 +2366,160 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J11" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.438</v>
+        <v>0.445</v>
       </c>
       <c r="L11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="M11" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.272</v>
+        <v>0.283</v>
       </c>
       <c r="O11" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="P11" t="n">
-        <v>24.3</v>
+        <v>25.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.763</v>
+        <v>0.724</v>
       </c>
       <c r="R11" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>33.7</v>
       </c>
       <c r="T11" t="n">
-        <v>43.8</v>
+        <v>45.7</v>
       </c>
       <c r="U11" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="V11" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="W11" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.8</v>
+        <v>22.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>97</v>
+        <v>96.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>7.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
         <v>7</v>
       </c>
       <c r="AI11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AM11" t="n">
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>19</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AR11" t="n">
         <v>12</v>
       </c>
       <c r="AS11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
         <v>13</v>
       </c>
-      <c r="AT11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>15</v>
-      </c>
       <c r="AV11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AX11" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AY11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ11" t="n">
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>7</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2592,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP12" t="n">
         <v>13</v>
@@ -2619,7 +2686,7 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY12" t="n">
         <v>21</v>
@@ -2634,7 +2701,7 @@
         <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2811,7 @@
         <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH14" t="n">
         <v>7</v>
@@ -2944,7 +3011,7 @@
         <v>19</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
         <v>26</v>
@@ -2953,7 +3020,7 @@
         <v>28</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3190,7 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK15" t="n">
         <v>5</v>
@@ -3144,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
         <v>30</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
         <v>23</v>
@@ -3165,7 +3232,7 @@
         <v>26</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
         <v>5</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-5</v>
       </c>
       <c r="AD16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
         <v>22</v>
@@ -3305,7 +3372,7 @@
         <v>24</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK16" t="n">
         <v>26</v>
@@ -3335,7 +3402,7 @@
         <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>21</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3763,7 @@
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="n">
         <v>21</v>
@@ -3708,13 +3775,13 @@
         <v>4</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>-7.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH19" t="n">
         <v>2</v>
@@ -3863,7 +3930,7 @@
         <v>11</v>
       </c>
       <c r="AN19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>13</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -4066,7 +4133,7 @@
         <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
         <v>12</v>
@@ -4087,7 +4154,7 @@
         <v>16</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC20" t="n">
         <v>2</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4270,7 @@
         <v>17</v>
       </c>
       <c r="AF21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG21" t="n">
         <v>16</v>
@@ -4230,7 +4297,7 @@
         <v>2</v>
       </c>
       <c r="AO21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -4379,16 +4446,16 @@
         <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH22" t="n">
         <v>7</v>
@@ -4412,13 +4479,13 @@
         <v>3</v>
       </c>
       <c r="AO22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP22" t="n">
         <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-1</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>17</v>
@@ -4579,7 +4646,7 @@
         <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK23" t="n">
         <v>22</v>
@@ -4606,7 +4673,7 @@
         <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>-1</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH24" t="n">
         <v>7</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-12.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>22</v>
@@ -4970,7 +5037,7 @@
         <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
@@ -4988,7 +5055,7 @@
         <v>28</v>
       </c>
       <c r="AY25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ25" t="n">
         <v>2</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-17</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>22</v>
@@ -5128,7 +5195,7 @@
         <v>27</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
         <v>30</v>
@@ -5137,13 +5204,13 @@
         <v>30</v>
       </c>
       <c r="AN26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5307,10 +5374,10 @@
         <v>13</v>
       </c>
       <c r="AJ27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
         <v>2</v>
@@ -5325,7 +5392,7 @@
         <v>18</v>
       </c>
       <c r="AP27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ27" t="n">
         <v>10</v>
@@ -5337,7 +5404,7 @@
         <v>8</v>
       </c>
       <c r="AT27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU27" t="n">
         <v>7</v>
@@ -5349,7 +5416,7 @@
         <v>15</v>
       </c>
       <c r="AX27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-12.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>22</v>
@@ -5528,7 +5595,7 @@
         <v>29</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>14.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5692,13 +5759,13 @@
         <v>27</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
         <v>22</v>
       </c>
       <c r="AS29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT29" t="n">
         <v>25</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX29" t="n">
         <v>15</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5874,13 +5941,13 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
         <v>17</v>
@@ -5892,7 +5959,7 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX30" t="n">
         <v>24</v>
@@ -5910,7 +5977,7 @@
         <v>2</v>
       </c>
       <c r="BC30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-13.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>22</v>
@@ -6056,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>1</v>
       </c>
       <c r="AS31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT31" t="n">
         <v>3</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-5-2007-08</t>
+          <t>2007-11-05</t>
         </is>
       </c>
     </row>
